--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="253">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -778,9 +778,6 @@
   </si>
   <si>
     <t xml:space="preserve">دنگ سس </t>
-  </si>
-  <si>
-    <t>دنپ کشمش</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1355,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4613,23 +4610,17 @@
     <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f>B232+B235-C235</f>
-        <v>3190000</v>
-      </c>
-      <c r="B235" s="8">
-        <v>230000</v>
-      </c>
+        <v>2960000</v>
+      </c>
+      <c r="B235" s="8"/>
       <c r="C235" s="8"/>
-      <c r="D235" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>250</v>
-      </c>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
     </row>
     <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f>A235+B236-C236</f>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4639,7 +4630,7 @@
     <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" ref="A237:A254" si="10">A236+B237-C237</f>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4649,7 +4640,7 @@
     <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4659,7 +4650,7 @@
     <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4669,7 +4660,7 @@
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4679,7 +4670,7 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4689,7 +4680,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4699,7 +4690,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4709,7 +4700,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4719,7 +4710,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4729,7 +4720,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4739,7 +4730,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4749,7 +4740,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4759,7 +4750,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4769,7 +4760,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4779,7 +4770,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4789,7 +4780,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4799,7 +4790,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4809,7 +4800,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4819,7 +4810,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14388500</v>
+        <v>14158500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4830,7 +4821,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="255">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -778,6 +778,12 @@
   </si>
   <si>
     <t xml:space="preserve">دنگ سس </t>
+  </si>
+  <si>
+    <t>1405/07/02</t>
+  </si>
+  <si>
+    <t>پچ پچ</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1361,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4610,17 +4616,23 @@
     <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <f>B232+B235-C235</f>
-        <v>2960000</v>
-      </c>
-      <c r="B235" s="8"/>
+        <v>3010000</v>
+      </c>
+      <c r="B235" s="8">
+        <v>50000</v>
+      </c>
       <c r="C235" s="8"/>
-      <c r="D235" s="1"/>
-      <c r="E235" s="1"/>
+      <c r="D235" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f>A235+B236-C236</f>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -4630,7 +4642,7 @@
     <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" ref="A237:A254" si="10">A236+B237-C237</f>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4640,7 +4652,7 @@
     <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4650,7 +4662,7 @@
     <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4660,7 +4672,7 @@
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4670,7 +4682,7 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4680,7 +4692,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4690,7 +4702,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4700,7 +4712,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4710,7 +4722,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4720,7 +4732,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4730,7 +4742,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4740,7 +4752,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4750,7 +4762,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4760,7 +4772,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4770,7 +4782,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4780,7 +4792,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4790,7 +4802,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4800,7 +4812,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4810,7 +4822,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14158500</v>
+        <v>14208500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4821,7 +4833,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="256">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -784,6 +784,9 @@
   </si>
   <si>
     <t>پچ پچ</t>
+  </si>
+  <si>
+    <t>1405/07/04</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1364,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4632,17 +4635,23 @@
     <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <f>A235+B236-C236</f>
-        <v>3010000</v>
-      </c>
-      <c r="B236" s="8"/>
+        <v>3235000</v>
+      </c>
+      <c r="B236" s="8">
+        <v>225000</v>
+      </c>
       <c r="C236" s="8"/>
-      <c r="D236" s="1"/>
-      <c r="E236" s="1"/>
+      <c r="D236" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" ref="A237:A254" si="10">A236+B237-C237</f>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -4652,7 +4661,7 @@
     <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4662,7 +4671,7 @@
     <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4672,7 +4681,7 @@
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4682,7 +4691,7 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4692,7 +4701,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4702,7 +4711,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4712,7 +4721,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4722,7 +4731,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4732,7 +4741,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4742,7 +4751,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4752,7 +4761,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4762,7 +4771,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4772,7 +4781,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4782,7 +4791,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4792,7 +4801,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4802,7 +4811,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4812,7 +4821,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4822,7 +4831,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14208500</v>
+        <v>14433500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4833,7 +4842,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="257">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -787,6 +787,9 @@
   </si>
   <si>
     <t>1405/07/04</t>
+  </si>
+  <si>
+    <t>سیب موز</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1367,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4651,17 +4654,21 @@
     <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <f t="shared" ref="A237:A254" si="10">A236+B237-C237</f>
-        <v>3235000</v>
-      </c>
-      <c r="B237" s="8"/>
+        <v>3285000</v>
+      </c>
+      <c r="B237" s="8">
+        <v>50000</v>
+      </c>
       <c r="C237" s="8"/>
-      <c r="D237" s="1"/>
+      <c r="D237" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="E237" s="1"/>
     </row>
     <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -4671,7 +4678,7 @@
     <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4681,7 +4688,7 @@
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4691,7 +4698,7 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4701,7 +4708,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4711,7 +4718,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4721,7 +4728,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4731,7 +4738,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4741,7 +4748,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4751,7 +4758,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4761,7 +4768,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4771,7 +4778,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4781,7 +4788,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4791,7 +4798,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4801,7 +4808,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4811,7 +4818,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4821,7 +4828,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4831,7 +4838,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14433500</v>
+        <v>14483500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4842,7 +4849,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="258">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -790,6 +790,9 @@
   </si>
   <si>
     <t>سیب موز</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1370,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4668,17 +4671,23 @@
     <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B238" s="8"/>
-      <c r="C238" s="8"/>
-      <c r="D238" s="1"/>
-      <c r="E238" s="1"/>
+      <c r="C238" s="8">
+        <v>80000</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -4688,7 +4697,7 @@
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4698,7 +4707,7 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4708,7 +4717,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4718,7 +4727,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4728,7 +4737,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4738,7 +4747,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4748,7 +4757,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4758,7 +4767,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4768,7 +4777,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4778,7 +4787,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4788,7 +4797,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4798,7 +4807,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4808,7 +4817,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4818,7 +4827,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4828,7 +4837,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4842,14 +4851,14 @@
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
-        <v>11198500</v>
+        <v>11278500</v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="259">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -793,6 +793,9 @@
   </si>
   <si>
     <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>1405/07/07</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1373,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4687,17 +4690,23 @@
     <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
-      </c>
-      <c r="B239" s="8"/>
+        <v>3221000</v>
+      </c>
+      <c r="B239" s="8">
+        <v>16000</v>
+      </c>
       <c r="C239" s="8"/>
-      <c r="D239" s="1"/>
-      <c r="E239" s="1"/>
+      <c r="D239" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -4707,7 +4716,7 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4717,7 +4726,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4727,7 +4736,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4737,7 +4746,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4747,7 +4756,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4757,7 +4766,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4767,7 +4776,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4777,7 +4786,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4787,7 +4796,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4797,7 +4806,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4807,7 +4816,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4817,7 +4826,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4827,7 +4836,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4837,7 +4846,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4847,7 +4856,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14483500</v>
+        <v>14499500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4858,7 +4867,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="260">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -796,6 +796,9 @@
   </si>
   <si>
     <t>1405/07/07</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1376,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4706,17 +4709,23 @@
     <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
-      </c>
-      <c r="B240" s="8"/>
+        <v>3285000</v>
+      </c>
+      <c r="B240" s="8">
+        <v>64000</v>
+      </c>
       <c r="C240" s="8"/>
-      <c r="D240" s="1"/>
-      <c r="E240" s="1"/>
+      <c r="D240" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -4726,7 +4735,7 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4736,7 +4745,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4746,7 +4755,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4756,7 +4765,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4766,7 +4775,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4776,7 +4785,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4786,7 +4795,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4796,7 +4805,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4806,7 +4815,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4816,7 +4825,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4826,7 +4835,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4836,7 +4845,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4846,7 +4855,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4856,7 +4865,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14499500</v>
+        <v>14563500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4867,7 +4876,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="260">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4725,17 +4725,21 @@
     <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
-      </c>
-      <c r="B241" s="8"/>
+        <v>3485000</v>
+      </c>
+      <c r="B241" s="8">
+        <v>200000</v>
+      </c>
       <c r="C241" s="8"/>
-      <c r="D241" s="1"/>
+      <c r="D241" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="E241" s="1"/>
     </row>
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4745,7 +4749,7 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4755,7 +4759,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4765,7 +4769,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4775,7 +4779,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4785,7 +4789,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4795,7 +4799,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4805,7 +4809,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4815,7 +4819,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4825,7 +4829,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4835,7 +4839,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4845,7 +4849,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4855,7 +4859,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4865,7 +4869,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14563500</v>
+        <v>14763500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4876,7 +4880,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="261">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -799,6 +799,9 @@
   </si>
   <si>
     <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>1405/07/14</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1379,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4739,17 +4742,23 @@
     <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B242" s="8"/>
-      <c r="C242" s="8"/>
-      <c r="D242" s="1"/>
-      <c r="E242" s="1"/>
+      <c r="C242" s="8">
+        <v>1500000</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4759,7 +4768,7 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4769,7 +4778,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4779,7 +4788,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4789,7 +4798,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4799,7 +4808,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4809,7 +4818,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4819,7 +4828,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4829,7 +4838,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4839,7 +4848,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4849,7 +4858,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4859,7 +4868,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4873,14 +4882,14 @@
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
-        <v>11278500</v>
+        <v>12778500</v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="262">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -802,6 +802,9 @@
   </si>
   <si>
     <t>1405/07/14</t>
+  </si>
+  <si>
+    <t>1304/07/16</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1382,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4758,17 +4761,23 @@
     <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
-      </c>
-      <c r="B243" s="8"/>
+        <v>2025000</v>
+      </c>
+      <c r="B243" s="8">
+        <v>40000</v>
+      </c>
       <c r="C243" s="8"/>
-      <c r="D243" s="1"/>
-      <c r="E243" s="1"/>
+      <c r="D243" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4778,7 +4787,7 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4788,7 +4797,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4798,7 +4807,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4808,7 +4817,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4818,7 +4827,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4828,7 +4837,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4838,7 +4847,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4848,7 +4857,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4858,7 +4867,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4868,7 +4877,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4878,7 +4887,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14763500</v>
+        <v>14803500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4889,7 +4898,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="263">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -804,7 +804,10 @@
     <t>1405/07/14</t>
   </si>
   <si>
-    <t>1304/07/16</t>
+    <t>1404/07/16</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1385,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4777,17 +4780,23 @@
     <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
-      </c>
-      <c r="B244" s="8"/>
+        <v>2250000</v>
+      </c>
+      <c r="B244" s="8">
+        <v>225000</v>
+      </c>
       <c r="C244" s="8"/>
-      <c r="D244" s="1"/>
-      <c r="E244" s="1"/>
+      <c r="D244" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4797,7 +4806,7 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4807,7 +4816,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4817,7 +4826,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4827,7 +4836,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4837,7 +4846,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4847,7 +4856,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4857,7 +4866,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4867,7 +4876,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4877,7 +4886,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4887,7 +4896,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>14803500</v>
+        <v>15028500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4898,7 +4907,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="265">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -808,6 +808,12 @@
   </si>
   <si>
     <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/07/19</t>
+  </si>
+  <si>
+    <t>عطر</t>
   </si>
 </sst>
 </file>
@@ -1385,7 +1391,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4796,17 +4802,23 @@
     <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
-      </c>
-      <c r="B245" s="8"/>
+        <v>2430000</v>
+      </c>
+      <c r="B245" s="8">
+        <v>180000</v>
+      </c>
       <c r="C245" s="8"/>
-      <c r="D245" s="1"/>
-      <c r="E245" s="1"/>
+      <c r="D245" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4816,7 +4828,7 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4826,7 +4838,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4836,7 +4848,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4846,7 +4858,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4856,7 +4868,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4866,7 +4878,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4876,7 +4888,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4886,7 +4898,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4896,7 +4908,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>15028500</v>
+        <v>15208500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4907,7 +4919,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -814,6 +814,9 @@
   </si>
   <si>
     <t>عطر</t>
+  </si>
+  <si>
+    <t>1405/07/21</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1394,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4818,17 +4821,23 @@
     <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
-      </c>
-      <c r="B246" s="8"/>
+        <v>2730000</v>
+      </c>
+      <c r="B246" s="8">
+        <v>300000</v>
+      </c>
       <c r="C246" s="8"/>
-      <c r="D246" s="1"/>
-      <c r="E246" s="1"/>
+      <c r="D246" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4838,7 +4847,7 @@
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4848,7 +4857,7 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4858,7 +4867,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4868,7 +4877,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4878,7 +4887,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4888,7 +4897,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4898,7 +4907,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4908,7 +4917,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>15208500</v>
+        <v>15508500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4919,7 +4928,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="269">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -817,6 +817,15 @@
   </si>
   <si>
     <t>1405/07/21</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>دنگ مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>آبمیوه</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1403,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4837,27 +4846,39 @@
     <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
-      </c>
-      <c r="B247" s="8"/>
+        <v>2919000</v>
+      </c>
+      <c r="B247" s="8">
+        <v>189000</v>
+      </c>
       <c r="C247" s="8"/>
-      <c r="D247" s="1"/>
-      <c r="E247" s="1"/>
+      <c r="D247" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
-      </c>
-      <c r="B248" s="8"/>
+        <v>2974000</v>
+      </c>
+      <c r="B248" s="8">
+        <v>55000</v>
+      </c>
       <c r="C248" s="8"/>
-      <c r="D248" s="1"/>
-      <c r="E248" s="1"/>
+      <c r="D248" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4867,7 +4888,7 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4877,7 +4898,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4887,7 +4908,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4897,7 +4918,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4907,7 +4928,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4917,7 +4938,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>15508500</v>
+        <v>15752500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4928,7 +4949,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="270">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -826,6 +826,9 @@
   </si>
   <si>
     <t>آبمیوه</t>
+  </si>
+  <si>
+    <t>1405/07/25</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1406,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4878,17 +4881,23 @@
     <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" si="10"/>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="B249" s="8"/>
-      <c r="C249" s="8"/>
-      <c r="D249" s="1"/>
-      <c r="E249" s="1"/>
+      <c r="C249" s="8">
+        <v>164000</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4898,7 +4907,7 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4908,7 +4917,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4918,7 +4927,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4928,7 +4937,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4942,14 +4951,14 @@
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
-        <v>12778500</v>
+        <v>12942500</v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="272">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -829,6 +829,12 @@
   </si>
   <si>
     <t>1405/07/25</t>
+  </si>
+  <si>
+    <t>1405/07/27</t>
+  </si>
+  <si>
+    <t>ویفر</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1412,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4897,17 +4903,23 @@
     <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="10"/>
-        <v>2810000</v>
-      </c>
-      <c r="B250" s="8"/>
+        <v>2845000</v>
+      </c>
+      <c r="B250" s="8">
+        <v>35000</v>
+      </c>
       <c r="C250" s="8"/>
-      <c r="D250" s="1"/>
-      <c r="E250" s="1"/>
+      <c r="D250" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4917,7 +4929,7 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4927,7 +4939,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4937,7 +4949,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4947,7 +4959,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>15752500</v>
+        <v>15787500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4958,7 +4970,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="273">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -835,6 +835,9 @@
   </si>
   <si>
     <t>ویفر</t>
+  </si>
+  <si>
+    <t>1405/07/29</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1415,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>2845000</v>
+        <v>3115000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4919,17 +4922,23 @@
     <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="10"/>
-        <v>2845000</v>
-      </c>
-      <c r="B251" s="8"/>
+        <v>3115000</v>
+      </c>
+      <c r="B251" s="8">
+        <v>270000</v>
+      </c>
       <c r="C251" s="8"/>
-      <c r="D251" s="1"/>
-      <c r="E251" s="1"/>
+      <c r="D251" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>2845000</v>
+        <v>3115000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4939,7 +4948,7 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>2845000</v>
+        <v>3115000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4949,7 +4958,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>2845000</v>
+        <v>3115000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4959,7 +4968,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>15787500</v>
+        <v>16057500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4970,7 +4979,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>2845000</v>
+        <v>3115000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="274">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -838,6 +838,9 @@
   </si>
   <si>
     <t>1405/07/29</t>
+  </si>
+  <si>
+    <t>1405/08/01</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1418,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3115000</v>
+        <v>3205000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4938,17 +4941,23 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3115000</v>
-      </c>
-      <c r="B252" s="8"/>
+        <v>3205000</v>
+      </c>
+      <c r="B252" s="8">
+        <v>90000</v>
+      </c>
       <c r="C252" s="8"/>
-      <c r="D252" s="1"/>
-      <c r="E252" s="1"/>
+      <c r="D252" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3115000</v>
+        <v>3205000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4958,7 +4967,7 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3115000</v>
+        <v>3205000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4968,7 +4977,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>16057500</v>
+        <v>16147500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4979,7 +4988,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3115000</v>
+        <v>3205000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="275">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -841,6 +841,9 @@
   </si>
   <si>
     <t>1405/08/01</t>
+  </si>
+  <si>
+    <t>1405/08/04</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1421,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3205000</v>
+        <v>3250000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4941,10 +4944,10 @@
     <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3250000</v>
       </c>
       <c r="B252" s="8">
-        <v>90000</v>
+        <v>135000</v>
       </c>
       <c r="C252" s="8"/>
       <c r="D252" s="1" t="s">
@@ -4957,17 +4960,21 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3250000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
-      <c r="D253" s="1"/>
-      <c r="E253" s="1"/>
+      <c r="D253" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3205000</v>
+        <v>3250000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4977,7 +4984,7 @@
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>16147500</v>
+        <v>16192500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4988,7 +4995,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3205000</v>
+        <v>3250000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="277">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -844,6 +844,12 @@
   </si>
   <si>
     <t>1405/08/04</t>
+  </si>
+  <si>
+    <t>1405/08/07</t>
+  </si>
+  <si>
+    <t>دنگ مزه ودکا</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1427,7 @@
       </c>
       <c r="H2" s="9">
         <f>B257</f>
-        <v>3250000</v>
+        <v>3510000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4960,9 +4966,11 @@
     <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="10"/>
-        <v>3250000</v>
-      </c>
-      <c r="B253" s="8"/>
+        <v>3385000</v>
+      </c>
+      <c r="B253" s="8">
+        <v>135000</v>
+      </c>
       <c r="C253" s="8"/>
       <c r="D253" s="1" t="s">
         <v>143</v>
@@ -4974,17 +4982,23 @@
     <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="10"/>
-        <v>3250000</v>
-      </c>
-      <c r="B254" s="8"/>
+        <v>3510000</v>
+      </c>
+      <c r="B254" s="8">
+        <v>125000</v>
+      </c>
       <c r="C254" s="8"/>
-      <c r="D254" s="1"/>
-      <c r="E254" s="1"/>
+      <c r="D254" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" s="9">
         <f>SUM(B235:B254)+B230</f>
-        <v>16192500</v>
+        <v>16452500</v>
       </c>
       <c r="C255" s="9">
         <f>SUM(C235:C254)+C230</f>
@@ -4995,7 +5009,7 @@
     <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="10">
         <f>A254</f>
-        <v>3250000</v>
+        <v>3510000</v>
       </c>
       <c r="C257" s="12" t="s">
         <v>198</v>
